--- a/Uploads/francais_valide.xlsx
+++ b/Uploads/francais_valide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8444E5-FCAE-49FC-B7BC-F65CA4458195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5465AA-9E3A-490C-A1A6-4388E6EA234C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -685,9 +685,6 @@
     <t>610</t>
   </si>
   <si>
-    <t xml:space="preserve">Numero_Dossier </t>
-  </si>
-  <si>
     <t>Appelant</t>
   </si>
   <si>
@@ -833,6 +830,9 @@
   </si>
   <si>
     <t>Date_Reception_Comptable_Copie_Decision</t>
+  </si>
+  <si>
+    <t>Numero_Dossier</t>
   </si>
 </sst>
 </file>
@@ -1221,214 +1221,214 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="19.1796875" customWidth="1"/>
-    <col min="5" max="5" width="30.7265625" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" customWidth="1"/>
-    <col min="7" max="7" width="35.6328125" customWidth="1"/>
-    <col min="8" max="8" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="41.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="37.81640625" customWidth="1"/>
-    <col min="11" max="11" width="32.26953125" customWidth="1"/>
-    <col min="12" max="12" width="28.26953125" customWidth="1"/>
-    <col min="13" max="13" width="28.7265625" customWidth="1"/>
-    <col min="14" max="14" width="35.26953125" customWidth="1"/>
-    <col min="15" max="15" width="23.90625" customWidth="1"/>
-    <col min="16" max="16" width="26.26953125" customWidth="1"/>
-    <col min="17" max="17" width="47.81640625" customWidth="1"/>
-    <col min="18" max="18" width="36.54296875" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" customWidth="1"/>
+    <col min="11" max="11" width="32.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
+    <col min="13" max="13" width="28.7109375" customWidth="1"/>
+    <col min="14" max="14" width="35.28515625" customWidth="1"/>
+    <col min="15" max="15" width="23.85546875" customWidth="1"/>
+    <col min="16" max="16" width="26.28515625" customWidth="1"/>
+    <col min="17" max="17" width="47.85546875" customWidth="1"/>
+    <col min="18" max="18" width="36.5703125" customWidth="1"/>
     <col min="19" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="39.26953125" customWidth="1"/>
-    <col min="21" max="21" width="53.1796875" customWidth="1"/>
-    <col min="22" max="22" width="39.1796875" customWidth="1"/>
-    <col min="23" max="23" width="29.36328125" customWidth="1"/>
-    <col min="24" max="24" width="28.453125" customWidth="1"/>
-    <col min="25" max="25" width="50.08984375" customWidth="1"/>
-    <col min="26" max="26" width="37.90625" customWidth="1"/>
-    <col min="27" max="27" width="31.6328125" customWidth="1"/>
+    <col min="20" max="20" width="39.28515625" customWidth="1"/>
+    <col min="21" max="21" width="53.140625" customWidth="1"/>
+    <col min="22" max="22" width="39.140625" customWidth="1"/>
+    <col min="23" max="23" width="29.42578125" customWidth="1"/>
+    <col min="24" max="24" width="28.42578125" customWidth="1"/>
+    <col min="25" max="25" width="50.140625" customWidth="1"/>
+    <col min="26" max="26" width="37.85546875" customWidth="1"/>
+    <col min="27" max="27" width="31.5703125" customWidth="1"/>
     <col min="28" max="28" width="36" customWidth="1"/>
-    <col min="29" max="29" width="33.6328125" customWidth="1"/>
-    <col min="30" max="30" width="37.08984375" customWidth="1"/>
-    <col min="31" max="31" width="38.1796875" customWidth="1"/>
-    <col min="32" max="32" width="36.90625" customWidth="1"/>
-    <col min="33" max="33" width="49.26953125" customWidth="1"/>
-    <col min="34" max="34" width="42.453125" customWidth="1"/>
-    <col min="35" max="35" width="34.1796875" customWidth="1"/>
-    <col min="36" max="36" width="38.08984375" customWidth="1"/>
-    <col min="37" max="37" width="53.453125" customWidth="1"/>
-    <col min="38" max="38" width="38.6328125" customWidth="1"/>
-    <col min="39" max="39" width="32.90625" customWidth="1"/>
-    <col min="40" max="40" width="41.81640625" customWidth="1"/>
-    <col min="41" max="41" width="35.26953125" customWidth="1"/>
-    <col min="42" max="42" width="38.6328125" customWidth="1"/>
+    <col min="29" max="29" width="33.5703125" customWidth="1"/>
+    <col min="30" max="30" width="37.140625" customWidth="1"/>
+    <col min="31" max="31" width="38.140625" customWidth="1"/>
+    <col min="32" max="32" width="36.85546875" customWidth="1"/>
+    <col min="33" max="33" width="49.28515625" customWidth="1"/>
+    <col min="34" max="34" width="42.42578125" customWidth="1"/>
+    <col min="35" max="35" width="34.140625" customWidth="1"/>
+    <col min="36" max="36" width="38.140625" customWidth="1"/>
+    <col min="37" max="37" width="53.42578125" customWidth="1"/>
+    <col min="38" max="38" width="38.5703125" customWidth="1"/>
+    <col min="39" max="39" width="32.85546875" customWidth="1"/>
+    <col min="40" max="40" width="41.85546875" customWidth="1"/>
+    <col min="41" max="41" width="35.28515625" customWidth="1"/>
+    <col min="42" max="42" width="38.5703125" customWidth="1"/>
     <col min="43" max="43" width="41" customWidth="1"/>
-    <col min="44" max="44" width="38.36328125" customWidth="1"/>
-    <col min="45" max="45" width="37.36328125" customWidth="1"/>
-    <col min="46" max="46" width="29.90625" customWidth="1"/>
-    <col min="47" max="47" width="28.7265625" customWidth="1"/>
+    <col min="44" max="44" width="38.42578125" customWidth="1"/>
+    <col min="45" max="45" width="37.42578125" customWidth="1"/>
+    <col min="46" max="46" width="29.85546875" customWidth="1"/>
+    <col min="47" max="47" width="28.7109375" customWidth="1"/>
     <col min="48" max="48" width="40" customWidth="1"/>
-    <col min="49" max="49" width="33.08984375" customWidth="1"/>
-    <col min="50" max="50" width="38.1796875" customWidth="1"/>
-    <col min="51" max="51" width="8.7265625" customWidth="1"/>
+    <col min="49" max="49" width="33.140625" customWidth="1"/>
+    <col min="50" max="50" width="38.140625" customWidth="1"/>
+    <col min="51" max="51" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="AX1" s="4" t="s">
-        <v>270</v>
-      </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>88</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>107</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>126</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>145</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>164</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>183</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>202</v>
       </c>

--- a/Uploads/francais_valide.xlsx
+++ b/Uploads/francais_valide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5465AA-9E3A-490C-A1A6-4388E6EA234C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D1EA3B-6F46-4712-B997-F334C0FBA053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="273">
   <si>
     <t>1</t>
   </si>
@@ -34,9 +34,6 @@
     <t>2024-09-01</t>
   </si>
   <si>
-    <t>جهة 1</t>
-  </si>
-  <si>
     <t>مركز 1</t>
   </si>
   <si>
@@ -694,9 +691,6 @@
     <t>Emis_En_Date_Du</t>
   </si>
   <si>
-    <t>IdCRC</t>
-  </si>
-  <si>
     <t>Centre_Comptable</t>
   </si>
   <si>
@@ -833,6 +827,18 @@
   </si>
   <si>
     <t>Numero_Dossier</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>Cour régionale des comptes de Rabat-Salé-Kénitra</t>
+  </si>
+  <si>
+    <t>Cour régionale des comptes de Casablanca-Settat</t>
+  </si>
+  <si>
+    <t>Cour régionale des comptes de Dakhla-Oued Ed-Dahab</t>
   </si>
 </sst>
 </file>
@@ -1223,11 +1229,11 @@
   <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="49.42578125" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="5" max="5" width="67" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="35.5703125" customWidth="1"/>
     <col min="8" max="8" width="27.140625" customWidth="1"/>
@@ -1278,154 +1284,154 @@
   <sheetData>
     <row r="1" spans="1:50" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="AW1" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
@@ -1442,1510 +1448,1510 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AG2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AM2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AN2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AO2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AR2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AT2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AU2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AV2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW2" s="3" t="s">
+      <c r="AX2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="AX2" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AJ3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AJ3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV3" s="1" t="s">
+      <c r="AW3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AW3" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="AX3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AC4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AJ4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AJ4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV4" s="1" t="s">
+      <c r="AW4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AW4" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="AX4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="U5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AA5" s="2" t="s">
+      <c r="AB5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="2" t="s">
+      <c r="AC5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AC5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI5" s="1" t="s">
+      <c r="AJ5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV5" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AJ5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV5" s="1" t="s">
+      <c r="AW5" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AW5" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="AX5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI6" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AC6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI6" s="1" t="s">
+      <c r="AJ6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV6" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="AJ6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV6" s="1" t="s">
+      <c r="AW6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="AW6" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="AX6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="U7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI7" s="1" t="s">
+      <c r="AJ7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV7" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AJ7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV7" s="1" t="s">
+      <c r="AW7" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AW7" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="AX7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI8" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI8" s="1" t="s">
+      <c r="AJ8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV8" s="1" t="s">
+      <c r="AW8" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AW8" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="AX8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I9" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AC9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI9" s="1" t="s">
+      <c r="AJ9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV9" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV9" s="1" t="s">
+      <c r="AW9" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AW9" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="AX9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="U10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI10" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI10" s="1" t="s">
+      <c r="AJ10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV10" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV10" s="1" t="s">
+      <c r="AW10" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="AW10" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="AX10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="I11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="U11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y11" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="U11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="Z11" s="2" t="s">
+      <c r="AA11" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="AA11" s="2" t="s">
+      <c r="AB11" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="AB11" s="2" t="s">
+      <c r="AC11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI11" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AC11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI11" s="1" t="s">
+      <c r="AJ11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV11" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="AJ11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV11" s="1" t="s">
+      <c r="AW11" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="AW11" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="AX11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/francais_valide.xlsx
+++ b/Uploads/francais_valide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D1EA3B-6F46-4712-B997-F334C0FBA053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186CF167-4E58-4333-9B5C-73D634C875E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="279">
   <si>
     <t>1</t>
   </si>
@@ -139,33 +139,15 @@
     <t>2024-09-21</t>
   </si>
   <si>
-    <t>2024-09-22</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
     <t>2024-09-24</t>
   </si>
   <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>2024-09-26</t>
-  </si>
-  <si>
     <t>2024-09-27</t>
   </si>
   <si>
-    <t>2024-09-28</t>
-  </si>
-  <si>
     <t>قرار 1</t>
   </si>
   <si>
-    <t>601</t>
-  </si>
-  <si>
     <t>2024-09-29</t>
   </si>
   <si>
@@ -223,9 +205,6 @@
     <t>قرار 2</t>
   </si>
   <si>
-    <t>602</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -280,9 +259,6 @@
     <t>قرار 3</t>
   </si>
   <si>
-    <t>603</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -337,9 +313,6 @@
     <t>قرار 4</t>
   </si>
   <si>
-    <t>604</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -394,9 +367,6 @@
     <t>قرار 5</t>
   </si>
   <si>
-    <t>605</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -451,9 +421,6 @@
     <t>قرار 6</t>
   </si>
   <si>
-    <t>606</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -508,9 +475,6 @@
     <t>قرار 7</t>
   </si>
   <si>
-    <t>607</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -565,9 +529,6 @@
     <t>قرار 8</t>
   </si>
   <si>
-    <t>608</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -622,9 +583,6 @@
     <t>قرار 9</t>
   </si>
   <si>
-    <t>609</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -679,9 +637,6 @@
     <t>قرار 10</t>
   </si>
   <si>
-    <t>610</t>
-  </si>
-  <si>
     <t>Appelant</t>
   </si>
   <si>
@@ -839,6 +794,69 @@
   </si>
   <si>
     <t>Cour régionale des comptes de Dakhla-Oued Ed-Dahab</t>
+  </si>
+  <si>
+    <t>convocation 1</t>
+  </si>
+  <si>
+    <t>convocation 2</t>
+  </si>
+  <si>
+    <t>convocation 3</t>
+  </si>
+  <si>
+    <t>convocation 4</t>
+  </si>
+  <si>
+    <t>convocation 5</t>
+  </si>
+  <si>
+    <t>convocation 6</t>
+  </si>
+  <si>
+    <t>convocation 7</t>
+  </si>
+  <si>
+    <t>convocation 8</t>
+  </si>
+  <si>
+    <t>convocation 9</t>
+  </si>
+  <si>
+    <t>convocation 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">convocation 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispositif Decision 1 </t>
+  </si>
+  <si>
+    <t>Dispositif Decision 2</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 3</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 4</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 5</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 6</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 7</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 8</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 9</t>
+  </si>
+  <si>
+    <t>Dispositif Decision 10</t>
   </si>
 </sst>
 </file>
@@ -848,7 +866,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -867,6 +885,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1235,16 +1259,16 @@
     <col min="4" max="4" width="33.5703125" customWidth="1"/>
     <col min="5" max="5" width="67" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" customWidth="1"/>
-    <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="37.85546875" customWidth="1"/>
-    <col min="11" max="11" width="32.28515625" customWidth="1"/>
+    <col min="7" max="7" width="59.140625" customWidth="1"/>
+    <col min="8" max="8" width="43" customWidth="1"/>
+    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="53.28515625" customWidth="1"/>
+    <col min="11" max="11" width="55.5703125" customWidth="1"/>
     <col min="12" max="12" width="28.28515625" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" customWidth="1"/>
-    <col min="14" max="14" width="35.28515625" customWidth="1"/>
+    <col min="13" max="13" width="66.5703125" customWidth="1"/>
+    <col min="14" max="14" width="65.42578125" customWidth="1"/>
     <col min="15" max="15" width="23.85546875" customWidth="1"/>
-    <col min="16" max="16" width="26.28515625" customWidth="1"/>
+    <col min="16" max="16" width="51.7109375" customWidth="1"/>
     <col min="17" max="17" width="47.85546875" customWidth="1"/>
     <col min="18" max="18" width="36.5703125" customWidth="1"/>
     <col min="19" max="19" width="42" customWidth="1"/>
@@ -1257,181 +1281,181 @@
     <col min="26" max="26" width="37.85546875" customWidth="1"/>
     <col min="27" max="27" width="31.5703125" customWidth="1"/>
     <col min="28" max="28" width="36" customWidth="1"/>
-    <col min="29" max="29" width="33.5703125" customWidth="1"/>
+    <col min="29" max="29" width="59.85546875" customWidth="1"/>
     <col min="30" max="30" width="37.140625" customWidth="1"/>
     <col min="31" max="31" width="38.140625" customWidth="1"/>
     <col min="32" max="32" width="36.85546875" customWidth="1"/>
     <col min="33" max="33" width="49.28515625" customWidth="1"/>
     <col min="34" max="34" width="42.42578125" customWidth="1"/>
-    <col min="35" max="35" width="34.140625" customWidth="1"/>
-    <col min="36" max="36" width="38.140625" customWidth="1"/>
+    <col min="35" max="35" width="50.85546875" customWidth="1"/>
+    <col min="36" max="36" width="57.42578125" customWidth="1"/>
     <col min="37" max="37" width="53.42578125" customWidth="1"/>
     <col min="38" max="38" width="38.5703125" customWidth="1"/>
     <col min="39" max="39" width="32.85546875" customWidth="1"/>
     <col min="40" max="40" width="41.85546875" customWidth="1"/>
-    <col min="41" max="41" width="35.28515625" customWidth="1"/>
-    <col min="42" max="42" width="38.5703125" customWidth="1"/>
+    <col min="41" max="41" width="62.85546875" customWidth="1"/>
+    <col min="42" max="42" width="58.7109375" customWidth="1"/>
     <col min="43" max="43" width="41" customWidth="1"/>
-    <col min="44" max="44" width="38.42578125" customWidth="1"/>
-    <col min="45" max="45" width="37.42578125" customWidth="1"/>
-    <col min="46" max="46" width="29.85546875" customWidth="1"/>
+    <col min="44" max="44" width="67.140625" customWidth="1"/>
+    <col min="45" max="45" width="76.140625" customWidth="1"/>
+    <col min="46" max="46" width="48.85546875" customWidth="1"/>
     <col min="47" max="47" width="28.7109375" customWidth="1"/>
     <col min="48" max="48" width="40" customWidth="1"/>
-    <col min="49" max="49" width="33.140625" customWidth="1"/>
-    <col min="50" max="50" width="38.140625" customWidth="1"/>
+    <col min="49" max="49" width="48.140625" customWidth="1"/>
+    <col min="50" max="50" width="56.28515625" customWidth="1"/>
     <col min="51" max="51" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AR1" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="AS1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="AT1" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="AV1" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="AW1" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
@@ -1448,7 +1472,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>4</v>
@@ -1556,51 +1580,51 @@
         <v>38</v>
       </c>
       <c r="AO2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AT2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AU2" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AV2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AW2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW2" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="AX2" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -1612,40 +1636,40 @@
         <v>6</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>19</v>
@@ -1660,16 +1684,16 @@
         <v>22</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>27</v>
@@ -1690,7 +1714,7 @@
         <v>32</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AJ3" s="3" t="s">
         <v>34</v>
@@ -1708,51 +1732,51 @@
         <v>38</v>
       </c>
       <c r="AO3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AR3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AU3" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="AX3" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
@@ -1764,40 +1788,40 @@
         <v>6</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>19</v>
@@ -1812,16 +1836,16 @@
         <v>22</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AC4" s="3" t="s">
         <v>27</v>
@@ -1842,7 +1866,7 @@
         <v>32</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ4" s="3" t="s">
         <v>34</v>
@@ -1860,51 +1884,51 @@
         <v>38</v>
       </c>
       <c r="AO4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP4" s="2" t="s">
+      <c r="AR4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AT4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR4" s="2" t="s">
+      <c r="AU4" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW4" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="AX4" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -1916,40 +1940,40 @@
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>19</v>
@@ -1964,16 +1988,16 @@
         <v>22</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AC5" s="3" t="s">
         <v>27</v>
@@ -1994,7 +2018,7 @@
         <v>32</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="AJ5" s="3" t="s">
         <v>34</v>
@@ -2012,51 +2036,51 @@
         <v>38</v>
       </c>
       <c r="AO5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AQ5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP5" s="2" t="s">
+      <c r="AR5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AT5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR5" s="2" t="s">
+      <c r="AU5" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AW5" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="AX5" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>4</v>
@@ -2068,40 +2092,40 @@
         <v>6</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>19</v>
@@ -2116,16 +2140,16 @@
         <v>22</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AC6" s="3" t="s">
         <v>27</v>
@@ -2146,7 +2170,7 @@
         <v>32</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="AJ6" s="3" t="s">
         <v>34</v>
@@ -2164,51 +2188,51 @@
         <v>38</v>
       </c>
       <c r="AO6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AQ6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP6" s="2" t="s">
+      <c r="AR6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AT6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR6" s="2" t="s">
+      <c r="AU6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="AV6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV6" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AW6" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="AX6" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>4</v>
@@ -2220,40 +2244,40 @@
         <v>6</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>19</v>
@@ -2268,16 +2292,16 @@
         <v>22</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AC7" s="3" t="s">
         <v>27</v>
@@ -2298,7 +2322,7 @@
         <v>32</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="AJ7" s="3" t="s">
         <v>34</v>
@@ -2316,51 +2340,51 @@
         <v>38</v>
       </c>
       <c r="AO7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP7" s="2" t="s">
+      <c r="AR7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AT7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AU7" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="AV7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV7" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AW7" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="AX7" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
@@ -2372,40 +2396,40 @@
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>19</v>
@@ -2420,16 +2444,16 @@
         <v>22</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>27</v>
@@ -2450,7 +2474,7 @@
         <v>32</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="AJ8" s="3" t="s">
         <v>34</v>
@@ -2468,51 +2492,51 @@
         <v>38</v>
       </c>
       <c r="AO8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AQ8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP8" s="2" t="s">
+      <c r="AR8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="AT8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR8" s="2" t="s">
+      <c r="AU8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="AV8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AW8" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="AX8" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>4</v>
@@ -2524,40 +2548,40 @@
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>19</v>
@@ -2572,16 +2596,16 @@
         <v>22</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>27</v>
@@ -2602,7 +2626,7 @@
         <v>32</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>34</v>
@@ -2620,51 +2644,51 @@
         <v>38</v>
       </c>
       <c r="AO9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP9" s="2" t="s">
+      <c r="AR9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AT9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR9" s="2" t="s">
+      <c r="AU9" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="AV9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AW9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV9" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AW9" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="AX9" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
@@ -2676,40 +2700,40 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>19</v>
@@ -2724,16 +2748,16 @@
         <v>22</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>27</v>
@@ -2754,7 +2778,7 @@
         <v>32</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>34</v>
@@ -2772,51 +2796,51 @@
         <v>38</v>
       </c>
       <c r="AO10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP10" s="2" t="s">
+      <c r="AR10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="AT10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR10" s="2" t="s">
+      <c r="AU10" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AV10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="AW10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV10" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AW10" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="AX10" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>4</v>
@@ -2828,40 +2852,40 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="U11" s="3" t="s">
         <v>19</v>
@@ -2876,16 +2900,16 @@
         <v>22</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="AC11" s="3" t="s">
         <v>27</v>
@@ -2906,7 +2930,7 @@
         <v>32</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="AJ11" s="3" t="s">
         <v>34</v>
@@ -2924,37 +2948,38 @@
         <v>38</v>
       </c>
       <c r="AO11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AQ11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP11" s="2" t="s">
+      <c r="AR11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="AT11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR11" s="2" t="s">
+      <c r="AU11" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="AV11" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AW11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="AW11" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="AX11" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>